--- a/examples/data/account_values.xlsx
+++ b/examples/data/account_values.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -442,6 +442,11 @@
           <t>account_value</t>
         </is>
       </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>guaranteed_credit_rate</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -459,6 +464,9 @@
       <c r="E2" t="n">
         <v>100000000</v>
       </c>
+      <c r="F2" t="n">
+        <v>0.02</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -476,6 +484,9 @@
       <c r="E3" t="n">
         <v>200000000</v>
       </c>
+      <c r="F3" t="n">
+        <v>0.02</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -492,6 +503,9 @@
       </c>
       <c r="E4" t="n">
         <v>50000000</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.02</v>
       </c>
     </row>
   </sheetData>

--- a/examples/data/account_values.xlsx
+++ b/examples/data/account_values.xlsx
@@ -429,7 +429,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>death_benefit</t>
+          <t>DEATH_GENERAL_benefit</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">

--- a/examples/data/account_values.xlsx
+++ b/examples/data/account_values.xlsx
@@ -429,7 +429,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>DEATH_GENERAL_benefit</t>
+          <t>DEATH_benefit</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">

--- a/examples/data/account_values.xlsx
+++ b/examples/data/account_values.xlsx
@@ -444,7 +444,7 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>guaranteed_credit_rate</t>
+          <t>minimum_crediting_rate</t>
         </is>
       </c>
     </row>
